--- a/Excel Projects/Candle Making.xlsx
+++ b/Excel Projects/Candle Making.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wille\Desktop\Excel Projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wille\Desktop\Projects-And-Code-Will-Martin\Excel Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8404A309-6E68-4B9C-BC8B-C3BDFD2FBC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB27C60-8B8F-4BEC-8A3F-87069E10BA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{EB9295E0-2A09-4C6A-B14D-2AA5A95FE70B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{EB9295E0-2A09-4C6A-B14D-2AA5A95FE70B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -299,10 +299,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -657,7 +657,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>13</v>
       </c>
       <c r="B3" t="s">
@@ -671,7 +671,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="19"/>
+      <c r="A4" s="18"/>
       <c r="B4" s="3">
         <v>700</v>
       </c>
@@ -683,7 +683,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B6" t="s">
@@ -700,7 +700,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="19"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="4">
         <v>2</v>
       </c>
@@ -720,7 +720,7 @@
       <c r="B8" s="3"/>
     </row>
     <row r="9" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
@@ -734,7 +734,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="19"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="5">
         <v>1</v>
       </c>
@@ -748,7 +748,7 @@
       <c r="E10" s="14"/>
     </row>
     <row r="12" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
@@ -762,7 +762,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="19"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="3">
         <v>25000</v>
       </c>
@@ -780,7 +780,7 @@
       <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -797,7 +797,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="19"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="2">
         <v>120</v>
       </c>
@@ -813,7 +813,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>50</v>
       </c>
       <c r="B18" t="s">
@@ -824,7 +824,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="19"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="7">
         <f>((B16+C16) / C13) + E16</f>
         <v>3.04</v>
@@ -835,7 +835,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="18" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -846,17 +846,17 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="19"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C22" s="9">
         <f>B22/60</f>
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -870,22 +870,22 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="19"/>
+      <c r="A25" s="18"/>
       <c r="B25" s="10">
         <f>B16*C22</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C25" s="11">
         <f>C22*C16</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D25" s="12">
         <f>C22*E16</f>
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="18" t="s">
         <v>55</v>
       </c>
       <c r="B27" t="s">
@@ -896,7 +896,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="19"/>
+      <c r="A28" s="18"/>
       <c r="B28">
         <v>10</v>
       </c>
@@ -906,7 +906,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="18" t="s">
         <v>16</v>
       </c>
       <c r="B30" t="s">
@@ -917,57 +917,57 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="19"/>
+      <c r="A31" s="18"/>
       <c r="B31" s="13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C31" s="11">
         <f>B31*C13</f>
-        <v>1470.5882352941176</v>
+        <v>735.29411764705878</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="19" t="s">
+      <c r="A33" s="18" t="s">
         <v>37</v>
       </c>
       <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
         <v>38</v>
       </c>
-      <c r="C33" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="19"/>
-      <c r="B34" s="11">
-        <f>C34*C13</f>
-        <v>305.3921568627452</v>
-      </c>
-      <c r="C34" s="16">
+      <c r="A34" s="18"/>
+      <c r="B34" s="16">
         <f>D13 +B10 + C10 +D10 +(B25 / C13) + (C25 / C13) +D25</f>
-        <v>4.1533333333333342</v>
+        <v>3.1400000000000006</v>
+      </c>
+      <c r="C34" s="11">
+        <f>B34*C13</f>
+        <v>230.88235294117652</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="18" t="s">
         <v>15</v>
       </c>
       <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" t="s">
         <v>29</v>
       </c>
-      <c r="C36" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="19"/>
+      <c r="A37" s="18"/>
       <c r="B37" s="11">
-        <f>(C13*B31) - B34</f>
-        <v>1165.1960784313724</v>
+        <f>B31-B34</f>
+        <v>6.8599999999999994</v>
       </c>
       <c r="C37" s="11">
-        <f>B31-C34</f>
-        <v>15.846666666666666</v>
+        <f>(C13*B31) - C34</f>
+        <v>504.41176470588226</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -977,7 +977,7 @@
       <c r="C38" s="20"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="18" t="s">
         <v>32</v>
       </c>
       <c r="B39" t="s">
@@ -985,38 +985,38 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="19"/>
+      <c r="A40" s="18"/>
       <c r="B40" s="14">
         <v>0.5</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" t="s">
         <v>29</v>
       </c>
-      <c r="C42" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="19"/>
+      <c r="A43" s="18"/>
       <c r="B43" s="11">
         <f>B37*B40</f>
-        <v>582.59803921568619</v>
+        <v>3.4299999999999997</v>
       </c>
       <c r="C43" s="11">
         <f>C37*B40</f>
-        <v>7.9233333333333329</v>
+        <v>252.20588235294113</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C47" s="18"/>
+      <c r="C47" s="19"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="1" t="s">
@@ -1031,8 +1031,8 @@
         <v>43</v>
       </c>
       <c r="C49" s="14">
-        <f>D13/$C$34</f>
-        <v>0.44783306581059384</v>
+        <f>D13/$B$34</f>
+        <v>0.59235668789808904</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.55000000000000004">
@@ -1040,8 +1040,8 @@
         <v>45</v>
       </c>
       <c r="C50" s="14">
-        <f>B10/$C$34</f>
-        <v>0.24077046548956657</v>
+        <f>B10/$B$34</f>
+        <v>0.31847133757961776</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.55000000000000004">
@@ -1049,8 +1049,8 @@
         <v>44</v>
       </c>
       <c r="C51" s="14">
-        <f>C10/$C$34</f>
-        <v>4.333868378812198E-2</v>
+        <f>C10/$B$34</f>
+        <v>5.7324840764331197E-2</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.55000000000000004">
@@ -1058,8 +1058,8 @@
         <v>57</v>
       </c>
       <c r="C52" s="14">
-        <f>D10/$C$34</f>
-        <v>2.4077046548956659E-2</v>
+        <f>D10/$B$34</f>
+        <v>3.1847133757961776E-2</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.55000000000000004">
@@ -1067,8 +1067,8 @@
         <v>58</v>
       </c>
       <c r="C53" s="14">
-        <f>(B25/$C$13)/$C$34</f>
-        <v>0.13097913322632421</v>
+        <f>(B25/$C$13)/$B$34</f>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.55000000000000004">
@@ -1076,8 +1076,8 @@
         <v>47</v>
       </c>
       <c r="C54" s="15">
-        <f>D25/$C$34</f>
-        <v>8.025682182985551E-2</v>
+        <f>D25/$B$34</f>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.55000000000000004">
@@ -1085,8 +1085,8 @@
         <v>46</v>
       </c>
       <c r="C55" s="14">
-        <f>(C25/$C$13)/$C$34</f>
-        <v>3.2744783306581052E-2</v>
+        <f>(C25/$C$13)/$B$34</f>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.55000000000000004">
@@ -1095,16 +1095,11 @@
       </c>
       <c r="C56" s="14">
         <f>SUM(C49:C55)</f>
-        <v>0.99999999999999989</v>
+        <v>0.99999999999999978</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A21:A22"/>
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A36:A37"/>
@@ -1116,6 +1111,11 @@
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A21:A22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
